--- a/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,98 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,65 +760,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E8" s="3">
         <v>78000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>75400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>71800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>72400</v>
       </c>
       <c r="H8" s="3">
         <v>72400</v>
       </c>
       <c r="I8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="J8" s="3">
         <v>68200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>66100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>64900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>59300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>49000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>39700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>69500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>33200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>112100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>25600</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,65 +834,68 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E9" s="3">
         <v>19100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5900</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,65 +908,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E10" s="3">
         <v>58900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>54400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>53900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>49000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>37500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>54200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>85100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,65 +1012,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E12" s="3">
         <v>21700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>22300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>43100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10800</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,44 +1158,47 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E14" s="3">
         <v>6900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>4100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1195,8 +1214,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1213,13 +1232,16 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="E15" s="3">
         <v>2000</v>
@@ -1240,14 +1262,14 @@
         <v>2000</v>
       </c>
       <c r="K15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L15" s="3">
         <v>1900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1400</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,8 +1285,8 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1284,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,65 +1333,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E17" s="3">
         <v>100200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>96300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>95400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>107100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>103000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>107300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>102200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>98700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>80600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>84300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>40600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>153100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35900</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,65 +1405,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-20900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-23600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-34700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-39100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10300</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,65 +1509,66 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>2700</v>
       </c>
       <c r="E20" s="3">
         <v>2800</v>
       </c>
       <c r="F20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,65 +1581,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-16300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-15200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-18300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-29200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-36000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-33400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-19200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-38400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1655,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,35 +1688,35 @@
         <v>700</v>
       </c>
       <c r="L22" s="3">
+        <v>700</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1690,65 +1729,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-20200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-18900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-36900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-21400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-42600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1761,41 +1803,44 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>200</v>
       </c>
       <c r="F24" s="3">
         <v>200</v>
       </c>
       <c r="G24" s="3">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1817,8 +1862,8 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1832,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,65 +1951,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-33000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-39600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-37000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-42600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10500</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,65 +2025,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-20300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-33000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-37000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-49900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12300</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,65 +2395,68 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="E32" s="3">
         <v>-2800</v>
       </c>
       <c r="F32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2400,65 +2469,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-20300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-33000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-39600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-37000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-49900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-12300</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,65 +2617,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-20300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-33000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-39600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-37000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-49900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-12300</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,59 +2828,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E41" s="3">
         <v>69800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>91600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>220600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>250900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>297600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>364900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>172900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>189600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>219400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>178800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>33000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,64 +2900,67 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E42" s="3">
         <v>195600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>222900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>221300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>211900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>206100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>138100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>125200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>102300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>43500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>30400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>18400</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2885,59 +2974,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E43" s="3">
         <v>51800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>52200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>59000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>41000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>33800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>22900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>21500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3048,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3027,59 +3122,62 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E45" s="3">
         <v>24400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>21600</v>
       </c>
       <c r="F45" s="3">
         <v>21600</v>
       </c>
       <c r="G45" s="3">
+        <v>21600</v>
+      </c>
+      <c r="H45" s="3">
         <v>18800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>9500</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3098,59 +3196,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E46" s="3">
         <v>341500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>371100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>362900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>374200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>375500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>420000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>433200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>454500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>460500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>243100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>245400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>254100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>212900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>56600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>58600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3240,59 +3344,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E48" s="3">
         <v>15200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21200</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3311,41 +3418,44 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E49" s="3">
         <v>71200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>73300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>75300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>77300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>79100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>81200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>75400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>77500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>76700</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3471,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3382,8 +3492,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,59 +3640,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E52" s="3">
         <v>8000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3788,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>444100</v>
+      </c>
+      <c r="E54" s="3">
         <v>436000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>467500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>461500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>474100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>481400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>528600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>535000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>555500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>560500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>266500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>268800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>276600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>235500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>79600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>82000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,59 +3920,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,19 +3992,22 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="F58" s="3">
+        <v>400</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
@@ -3891,8 +4024,8 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3904,16 +4037,16 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>11900</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>2200</v>
       </c>
       <c r="R58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>2200</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3933,59 +4066,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E59" s="3">
         <v>60400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>84600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>69900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>71800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>59100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>72300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>56900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>42900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>37300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>40100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>35000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>30400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,59 +4140,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E60" s="3">
         <v>67100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>91500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>77400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>78800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>66300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>78600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>64800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>62800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>48800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>42700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>45900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>52500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>33100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,41 +4214,44 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>339600</v>
+      </c>
+      <c r="E61" s="3">
         <v>339400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>339000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>338000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>337500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>337000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>336500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>336000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>335500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>335100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4117,17 +4259,17 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>10000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>69100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>69500</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4146,59 +4288,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E62" s="3">
         <v>9700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15700</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,59 +4584,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>418500</v>
+      </c>
+      <c r="E66" s="3">
         <v>416100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>440600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>427100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>428400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>416300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>443600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>425100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>417200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>399300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>59900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>77000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>122700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>118300</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4715,14 +4882,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>227500</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>225500</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4741,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4982,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-594700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-591500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-571200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-552100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-530000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-497000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-466700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-427100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-390100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-355800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-334200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-321900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-313400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-299200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-291100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-280700</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,59 +5278,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E76" s="3">
         <v>19900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>65100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>85000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>109900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>138300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>161200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>211100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>215300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>216800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>158500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-270500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-261700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,65 +5505,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-20300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-33000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-39600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-37000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-49900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-12300</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5385,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,40 +5609,41 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="3">
         <v>3100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2900</v>
       </c>
       <c r="F83" s="3">
         <v>2900</v>
       </c>
       <c r="G83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H83" s="3">
         <v>2800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2800</v>
       </c>
       <c r="J83" s="3">
         <v>2800</v>
       </c>
       <c r="K83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L83" s="3">
         <v>2600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>700</v>
       </c>
       <c r="N83" s="3">
         <v>700</v>
@@ -5457,20 +5655,20 @@
         <v>700</v>
       </c>
       <c r="Q83" s="3">
+        <v>700</v>
+      </c>
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5483,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-31400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>14700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-20800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-50800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-17000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-40000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11100</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,65 +6155,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1200</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6007,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,65 +6375,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E94" s="3">
         <v>26400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-69300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-60200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-94700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>17900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>11000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6220,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>300800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>44500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>160000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>35400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>35500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>17400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6847,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6673,65 +6921,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-119900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-46600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-67300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>192000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-29900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>40600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>153500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,68 +764,71 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>80400</v>
+      </c>
+      <c r="E8" s="3">
         <v>84100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>78000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>75400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>72400</v>
       </c>
       <c r="I8" s="3">
         <v>72400</v>
       </c>
       <c r="J8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="K8" s="3">
         <v>68200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>66100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>64900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>59300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>49000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>43100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>39700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>33200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>112100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>25600</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,68 +841,71 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E9" s="3">
         <v>18900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>17400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>15300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,68 +918,71 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E10" s="3">
         <v>65200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>56600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>53900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>54900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>51300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>49000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>37500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>32900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>54200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>85100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19700</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,68 +1026,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="3">
         <v>19500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>16500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>22300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>10900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10800</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,47 +1178,50 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1217,8 +1237,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1235,16 +1255,19 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2000</v>
       </c>
       <c r="F15" s="3">
         <v>2000</v>
@@ -1265,14 +1288,14 @@
         <v>2000</v>
       </c>
       <c r="L15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M15" s="3">
         <v>1900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1400</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,8 +1311,8 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,68 +1360,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E17" s="3">
         <v>89800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>100200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>96300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>95400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>107100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>103000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>107300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>102200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>98700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>80600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>61300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>84300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>153100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>35900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,68 +1435,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-22200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-20900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-23600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-34700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-30600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-39100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-21300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-8500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-41000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10300</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,68 +1543,69 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>2700</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2800</v>
       </c>
       <c r="F20" s="3">
         <v>2800</v>
       </c>
       <c r="G20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H20" s="3">
         <v>2400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,68 +1618,71 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-16300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-18300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-36000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-33400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-31200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-19200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-38400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9600</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,8 +1695,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1691,35 +1731,35 @@
         <v>700</v>
       </c>
       <c r="M22" s="3">
+        <v>700</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,68 +1772,71 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-20200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-21900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-30200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-21400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-42600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1806,44 +1849,47 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>200</v>
       </c>
       <c r="H24" s="3">
+        <v>200</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1865,8 +1911,8 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,68 +2003,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-33000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-39600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-37000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-42600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10500</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2028,68 +2080,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-20300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-33000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-39600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-37000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-49900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12300</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,68 +2465,71 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2700</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-2800</v>
       </c>
       <c r="F32" s="3">
         <v>-2800</v>
       </c>
       <c r="G32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,68 +2542,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-20300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-33000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-39600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-37000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-49900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-12300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,68 +2696,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-20300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-33000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-39600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-37000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-49900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-12300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2694,73 +2773,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,62 +2915,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E41" s="3">
         <v>71700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>69800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>91600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>220600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>250900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>297600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>364900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>172900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>189600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>219400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>178800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>25400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>33000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,67 +2990,70 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>204300</v>
+      </c>
+      <c r="E42" s="3">
         <v>198400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>195600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>222900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>221300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>211900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>206100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>138100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>125200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>102300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>43500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>30400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>18400</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2977,62 +3067,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E43" s="3">
         <v>37700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>52200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>59000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>41000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>33800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>29000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>26100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>20200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>16100</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,8 +3144,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3125,62 +3221,65 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E45" s="3">
         <v>34100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>21600</v>
       </c>
       <c r="G45" s="3">
         <v>21600</v>
       </c>
       <c r="H45" s="3">
+        <v>21600</v>
+      </c>
+      <c r="I45" s="3">
         <v>18800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>9500</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,62 +3298,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>343500</v>
+      </c>
+      <c r="E46" s="3">
         <v>342000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>341500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>371100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>362900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>374200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>375500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>420000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>433200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>454500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>460500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>243100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>245400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>254100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>212900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>56600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>58600</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3347,62 +3452,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E48" s="3">
         <v>14600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21200</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,44 +3529,47 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E49" s="3">
         <v>79100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>73300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>75300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>77300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>79100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>81200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>75400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>77500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>76700</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3585,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,62 +3760,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E52" s="3">
         <v>8300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,62 +3914,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>442500</v>
+      </c>
+      <c r="E54" s="3">
         <v>444100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>436000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>467500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>461500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>474100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>481400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>528600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>535000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>555500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>560500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>266500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>268800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>276600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>235500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>79600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>82000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,62 +4051,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E57" s="3">
         <v>8000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,22 +4126,25 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>600</v>
+      </c>
+      <c r="E58" s="3">
         <v>500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>400</v>
       </c>
       <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+      <c r="G58" s="3">
+        <v>400</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -4027,8 +4161,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -4040,16 +4174,16 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>11900</v>
-      </c>
-      <c r="R58" s="3">
-        <v>2200</v>
       </c>
       <c r="S58" s="3">
         <v>2200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>2200</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4069,62 +4203,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E59" s="3">
         <v>62200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>60400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>84600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>69900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>71800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>59100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>72300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>54600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>42900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>37300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>35400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>35000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>30400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,62 +4280,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E60" s="3">
         <v>70800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>67100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>91500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>77400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>78800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>66300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>78600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>62800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>42700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>40100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>45900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>52500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,44 +4357,47 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E61" s="3">
         <v>339600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>339400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>339000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>338000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>337500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>337000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>336500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>336000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>335500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>335100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4262,17 +4405,17 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>10000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>69100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69500</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4291,62 +4434,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E62" s="3">
         <v>8200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>28500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>12800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,62 +4742,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>415600</v>
+      </c>
+      <c r="E66" s="3">
         <v>418500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>416100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>440600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>427100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>428400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>416300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>443600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>425100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>417200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>399300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>59900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>77000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>122700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>118300</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,8 +5002,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4885,14 +5053,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>227500</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>225500</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,62 +5156,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-601100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-594700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-591500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-571200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-552100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-530000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-497000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-466700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-427100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-390100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-355800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-334200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-321900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-313400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-299200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-291100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-280700</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,62 +5464,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E76" s="3">
         <v>25500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>34400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>65100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>85000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>109900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>138300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>161200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>211100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>215300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>216800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>158500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-270500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-261700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5618,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,68 +5700,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-20300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-33000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-39600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-37000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-49900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-12300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,8 +5808,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5619,34 +5818,34 @@
         <v>3500</v>
       </c>
       <c r="E83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F83" s="3">
         <v>3100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2900</v>
       </c>
       <c r="G83" s="3">
         <v>2900</v>
       </c>
       <c r="H83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I83" s="3">
         <v>2800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2800</v>
       </c>
       <c r="K83" s="3">
         <v>2800</v>
       </c>
       <c r="L83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M83" s="3">
         <v>2600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>700</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
@@ -5658,20 +5857,20 @@
         <v>700</v>
       </c>
       <c r="R83" s="3">
+        <v>700</v>
+      </c>
+      <c r="S83" s="3">
         <v>1700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>500</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,68 +6268,71 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E89" s="3">
         <v>13300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-31400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-20800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-50800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-17000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-40000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11100</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,68 +6376,69 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,68 +6605,71 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-69300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-24800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-60200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-94700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>17900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>11000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6452,8 +6682,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,68 +7019,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>300800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>44500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>160000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>35400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>35500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>17400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,8 +7096,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6924,68 +7173,71 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-119900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-46600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>192000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>40600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>153500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
@@ -656,105 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,71 +768,74 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E8" s="3">
         <v>80400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>84100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>78000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>75400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>72400</v>
       </c>
       <c r="J8" s="3">
         <v>72400</v>
       </c>
       <c r="K8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="L8" s="3">
         <v>68200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>66100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>64900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>59300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>49000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>46700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>112100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25600</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,71 +848,74 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E9" s="3">
         <v>18400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>17400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>16900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>15300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -930,62 +940,62 @@
         <v>62000</v>
       </c>
       <c r="E10" s="3">
+        <v>62000</v>
+      </c>
+      <c r="F10" s="3">
         <v>65200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>53900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>54900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>51300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>49000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>48300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>37500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>32900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>54200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>85100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19700</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,71 +1040,72 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E12" s="3">
         <v>20000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>20800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>16500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>13500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>22300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>10900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>43100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10800</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,50 +1198,53 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>6300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1240,8 +1260,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1258,8 +1278,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1267,10 +1290,10 @@
         <v>2500</v>
       </c>
       <c r="E15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F15" s="3">
         <v>2300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2000</v>
       </c>
       <c r="G15" s="3">
         <v>2000</v>
@@ -1291,14 +1314,14 @@
         <v>2000</v>
       </c>
       <c r="M15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N15" s="3">
         <v>1900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1400</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,8 +1337,8 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1335,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,71 +1387,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E17" s="3">
         <v>88600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>89800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>100200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>95400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>107100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>103000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>107300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>102200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>98700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>80600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>61300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>49800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>84300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>153100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,71 +1465,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-8200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-5700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-22200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-23600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-34700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-30600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-39100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-7400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-41000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10300</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,71 +1577,72 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2800</v>
       </c>
       <c r="G20" s="3">
         <v>2800</v>
       </c>
       <c r="H20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I20" s="3">
         <v>2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,71 +1655,74 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-16300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-29200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-26500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-36000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-33400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-31200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-19200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-13000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-38400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1735,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,35 +1774,35 @@
         <v>700</v>
       </c>
       <c r="N22" s="3">
+        <v>700</v>
+      </c>
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1775,71 +1815,74 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-20200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-21900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-39600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-36900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-34500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-42600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,47 +1895,50 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>200</v>
       </c>
       <c r="H24" s="3">
         <v>200</v>
       </c>
       <c r="I24" s="3">
+        <v>200</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1914,8 +1960,8 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1975,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2055,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-22100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-33000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-39600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-37000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-34200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-42600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10500</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2135,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-20300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-22100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-33000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-39600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-37000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-49900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12300</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,71 +2535,74 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2800</v>
       </c>
       <c r="G32" s="3">
         <v>-2800</v>
       </c>
       <c r="H32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,71 +2615,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-22100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-33000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-39600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-37000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-49900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2775,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-22100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-33000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-39600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-37000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-49900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2855,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E41" s="3">
         <v>60900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>71700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>91600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>220600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>250900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>297600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>364900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>172900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>189600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>219400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>178800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>33000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,70 +3080,73 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E42" s="3">
         <v>204300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>198400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>195600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>222900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>221300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>211900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>206100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>138100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>125200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>102300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>43500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>30400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>18400</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3070,65 +3160,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E43" s="3">
         <v>39300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>37700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>52200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>59000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>51900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>48100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>45900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>41000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>33800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>26100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>16100</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3224,65 +3320,68 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E45" s="3">
         <v>39100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>24400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>21600</v>
       </c>
       <c r="H45" s="3">
         <v>21600</v>
       </c>
       <c r="I45" s="3">
+        <v>21600</v>
+      </c>
+      <c r="J45" s="3">
         <v>18800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>9500</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>355800</v>
+      </c>
+      <c r="E46" s="3">
         <v>343500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>342000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>341500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>371100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>362900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>374200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>375500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>420000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>433200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>454500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>460500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>243100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>245400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>254100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>212900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>56600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>58600</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3455,65 +3560,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>17600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21200</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,47 +3640,50 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E49" s="3">
         <v>76700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>73300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>75300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>77300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>79100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>81200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>75400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>77500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>76700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3699,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3609,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,65 +3880,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>452500</v>
+      </c>
+      <c r="E54" s="3">
         <v>442500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>444100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>436000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>467500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>461500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>474100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>481400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>528600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>535000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>555500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>560500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>266500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>268800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>276600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>235500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>79600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>82000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,65 +4182,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,25 +4260,28 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>400</v>
       </c>
       <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>400</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -4164,8 +4298,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4177,16 +4311,16 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>11900</v>
-      </c>
-      <c r="S58" s="3">
-        <v>2200</v>
       </c>
       <c r="T58" s="3">
         <v>2200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>2200</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4206,65 +4340,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E59" s="3">
         <v>60300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>62200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>60400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>69900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>71800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>59100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>54600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>37300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>35400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>40100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>35000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>30400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>24800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E60" s="3">
         <v>67900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>67100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>91500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>77400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>78800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>66300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>78600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>64800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>62800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>48800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>42700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>45900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>33100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,47 +4500,50 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>340500</v>
+      </c>
+      <c r="E61" s="3">
         <v>340000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>339600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>339400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>339000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>338000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>337500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>337000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>336500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>336000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>335500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>335100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4408,17 +4551,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>10000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>69500</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4437,65 +4580,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4514,8 +4660,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>426400</v>
+      </c>
+      <c r="E66" s="3">
         <v>415600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>418500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>416100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>440600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>427100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>428400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>416300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>443600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>425100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>417200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>399300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>59900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>77000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>122700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>118300</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5056,14 +5224,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>227500</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>225500</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -5082,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-612300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-601100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-594700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-591500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-571200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-552100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-530000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-497000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-466700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-427100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-390100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-355800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-334200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-321900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-313400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-299200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-291100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-280700</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E76" s="3">
         <v>26900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>34400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>65100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>85000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>109900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>138300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>161200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>211100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>215300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>216800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>158500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-270500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-261700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5810,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5895,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-22100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-33000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-39600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-37000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-49900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5821,34 +6020,34 @@
         <v>3500</v>
       </c>
       <c r="F83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G83" s="3">
         <v>3100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2900</v>
       </c>
       <c r="H83" s="3">
         <v>2900</v>
       </c>
       <c r="I83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J83" s="3">
         <v>2800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2800</v>
       </c>
       <c r="L83" s="3">
         <v>2800</v>
       </c>
       <c r="M83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="N83" s="3">
         <v>2600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
@@ -5860,20 +6059,20 @@
         <v>700</v>
       </c>
       <c r="S83" s="3">
+        <v>700</v>
+      </c>
+      <c r="T83" s="3">
         <v>1700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5886,8 +6085,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,71 +6485,74 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-31400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-20800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-50800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-40000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11100</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,71 +6597,72 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1200</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6454,8 +6675,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,71 +6835,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-69300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-24800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-60200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-94700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>17900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>11000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6685,8 +6915,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6791,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,71 +7265,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>300800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>44500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>160000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>35400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>35500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>17400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3400</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7176,71 +7425,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-10800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-30800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-119900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-46600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-67300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>192000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>40600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>153500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>BIGC</t>
   </si>
@@ -656,109 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -771,74 +772,77 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E8" s="3">
         <v>81800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>80400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>84100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>78000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>75400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>72400</v>
       </c>
       <c r="K8" s="3">
         <v>72400</v>
       </c>
       <c r="L8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="M8" s="3">
         <v>68200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>66100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>64900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>59300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>49000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>46700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>43100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>39700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>69500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>112100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>25600</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,74 +855,77 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E9" s="3">
         <v>19800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>18400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>19100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>17400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>16900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5900</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -931,74 +938,77 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>62000</v>
+        <v>63800</v>
       </c>
       <c r="E10" s="3">
         <v>62000</v>
       </c>
       <c r="F10" s="3">
+        <v>61900</v>
+      </c>
+      <c r="G10" s="3">
         <v>65200</v>
       </c>
-      <c r="G10" s="3">
-        <v>58900</v>
-      </c>
       <c r="H10" s="3">
-        <v>56600</v>
+        <v>59000</v>
       </c>
       <c r="I10" s="3">
-        <v>54400</v>
+        <v>56700</v>
       </c>
       <c r="J10" s="3">
+        <v>54300</v>
+      </c>
+      <c r="K10" s="3">
         <v>53900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>54900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>51300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>49000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>48300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>37500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>32900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>85100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19700</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1011,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1041,74 +1054,75 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E12" s="3">
         <v>20300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>16500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>13500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>22300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>10900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>43100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10800</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,8 +1135,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,53 +1218,56 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E14" s="3">
         <v>2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,8 +1283,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1281,22 +1301,25 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="E15" s="3">
         <v>2500</v>
       </c>
       <c r="F15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G15" s="3">
         <v>2300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2000</v>
       </c>
       <c r="H15" s="3">
         <v>2000</v>
@@ -1317,14 +1340,14 @@
         <v>2000</v>
       </c>
       <c r="N15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1400</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,8 +1363,8 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1361,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1388,74 +1414,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>95300</v>
+        <v>92700</v>
       </c>
       <c r="E17" s="3">
-        <v>88600</v>
+        <v>92400</v>
       </c>
       <c r="F17" s="3">
-        <v>89800</v>
+        <v>88300</v>
       </c>
       <c r="G17" s="3">
-        <v>100200</v>
+        <v>88700</v>
       </c>
       <c r="H17" s="3">
-        <v>96300</v>
+        <v>93400</v>
       </c>
       <c r="I17" s="3">
-        <v>95400</v>
+        <v>92200</v>
       </c>
       <c r="J17" s="3">
+        <v>90900</v>
+      </c>
+      <c r="K17" s="3">
         <v>107100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>103000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>107300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>102200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>98700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>80600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>61300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>49800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>84300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>40600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>153100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>35900</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1468,74 +1495,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-13500</v>
+        <v>-9000</v>
       </c>
       <c r="E18" s="3">
-        <v>-8200</v>
+        <v>-10600</v>
       </c>
       <c r="F18" s="3">
-        <v>-5700</v>
+        <v>-7900</v>
       </c>
       <c r="G18" s="3">
-        <v>-22200</v>
+        <v>-4500</v>
       </c>
       <c r="H18" s="3">
-        <v>-20900</v>
+        <v>-15300</v>
       </c>
       <c r="I18" s="3">
-        <v>-23600</v>
+        <v>-16800</v>
       </c>
       <c r="J18" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-34700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-39100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-14800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-7400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-41000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10300</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,8 +1578,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,74 +1611,75 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3100</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>2700</v>
       </c>
-      <c r="G20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>2400</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>4300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,74 +1692,77 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-6900</v>
+        <v>-6700</v>
       </c>
       <c r="E21" s="3">
-        <v>-1900</v>
+        <v>-8200</v>
       </c>
       <c r="F21" s="3">
-        <v>500</v>
+        <v>-5800</v>
       </c>
       <c r="G21" s="3">
-        <v>-16300</v>
+        <v>-2700</v>
       </c>
       <c r="H21" s="3">
-        <v>-15200</v>
+        <v>-13600</v>
       </c>
       <c r="I21" s="3">
-        <v>-18300</v>
+        <v>-14800</v>
       </c>
       <c r="J21" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-29200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-36000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-33400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-31200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-19200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-13000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-38400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9600</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1738,13 +1775,16 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>1900</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
@@ -1777,35 +1817,35 @@
         <v>700</v>
       </c>
       <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>400</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1818,74 +1858,77 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-20200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-21900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-32700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-36900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-34500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-12500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-42600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1898,50 +1941,53 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
-      </c>
-      <c r="H24" s="3">
-        <v>200</v>
       </c>
       <c r="I24" s="3">
         <v>200</v>
       </c>
       <c r="J24" s="3">
+        <v>200</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1963,8 +2009,8 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
@@ -1978,8 +2024,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,74 +2107,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-22100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-39600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-37000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-14200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-12500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-42600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10500</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,74 +2190,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-11300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-20300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-22100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-39600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-37000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-34200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-14200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-49900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12300</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,8 +2273,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2298,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2378,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2458,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2538,74 +2605,77 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3100</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2800</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-4300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2618,74 +2688,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-11300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-22100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-39600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-37000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-14200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-49900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12300</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2698,8 +2771,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2778,74 +2854,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-11300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-22100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-39600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-37000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-14200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-49900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12300</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,79 +2937,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2943,8 +3025,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2973,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3003,68 +3089,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E41" s="3">
         <v>133100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>61100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>220600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>250900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>297600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>364900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>172900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>189600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>219400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>178800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>33000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,73 +3170,76 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E42" s="3">
         <v>142700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>204300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>198400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>195600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>222900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>221300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>211900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>206100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>138100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>125200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>102300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>43500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>30400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>18400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3163,68 +3253,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E43" s="3">
         <v>45100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>39300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>37700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>51800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>52200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>59000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>51900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>41000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>29000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>26100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>22900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>21500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>20200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>16100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3243,31 +3336,34 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3323,68 +3419,71 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>34900</v>
+        <v>9100</v>
       </c>
       <c r="E45" s="3">
-        <v>39100</v>
+        <v>9100</v>
       </c>
       <c r="F45" s="3">
-        <v>34100</v>
+        <v>8700</v>
       </c>
       <c r="G45" s="3">
-        <v>24400</v>
+        <v>8300</v>
       </c>
       <c r="H45" s="3">
-        <v>21600</v>
+        <v>7600</v>
       </c>
       <c r="I45" s="3">
-        <v>21600</v>
+        <v>7000</v>
       </c>
       <c r="J45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="K45" s="3">
         <v>18800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>9500</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3403,68 +3502,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>243500</v>
+      </c>
+      <c r="E46" s="3">
         <v>355800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>343500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>342000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>341500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>371100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>362900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>374200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>375500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>420000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>433200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>454500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>460500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>243100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>245400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>254100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>212900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>56600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>58600</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3483,31 +3585,34 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3563,68 +3668,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E48" s="3">
         <v>13600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>17600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3643,50 +3751,53 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E49" s="3">
         <v>74100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>76700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>79100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>73300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>75300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>77300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>79100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>81200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>75400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>77500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>76700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,8 +3813,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3723,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3803,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3883,68 +4000,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>9000</v>
+        <v>2400</v>
       </c>
       <c r="E52" s="3">
-        <v>8200</v>
+        <v>2600</v>
       </c>
       <c r="F52" s="3">
-        <v>8300</v>
+        <v>1800</v>
       </c>
       <c r="G52" s="3">
-        <v>8000</v>
+        <v>1200</v>
       </c>
       <c r="H52" s="3">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="I52" s="3">
-        <v>7600</v>
+        <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>900</v>
+      </c>
+      <c r="K52" s="3">
         <v>7500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3963,8 +4083,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4043,68 +4166,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>335100</v>
+      </c>
+      <c r="E54" s="3">
         <v>452500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>442500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>444100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>436000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>467500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>461500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>474100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>481400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>528600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>535000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>555500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>560500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>266500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>268800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>276600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>235500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>79600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>82000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4249,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4153,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4183,68 +4313,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4263,31 +4394,34 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>3200</v>
       </c>
       <c r="E58" s="3">
-        <v>600</v>
+        <v>2800</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>3000</v>
       </c>
       <c r="G58" s="3">
-        <v>400</v>
+        <v>3100</v>
       </c>
       <c r="H58" s="3">
-        <v>400</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>2900</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2500</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -4301,8 +4435,8 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4314,16 +4448,16 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>11900</v>
-      </c>
-      <c r="T58" s="3">
-        <v>2200</v>
       </c>
       <c r="U58" s="3">
         <v>2200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>2200</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4343,68 +4477,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>71700</v>
+        <v>60900</v>
       </c>
       <c r="E59" s="3">
-        <v>60300</v>
+        <v>52000</v>
       </c>
       <c r="F59" s="3">
-        <v>62200</v>
+        <v>44000</v>
       </c>
       <c r="G59" s="3">
-        <v>60400</v>
+        <v>42300</v>
       </c>
       <c r="H59" s="3">
-        <v>84600</v>
+        <v>42300</v>
       </c>
       <c r="I59" s="3">
-        <v>69900</v>
+        <v>65800</v>
       </c>
       <c r="J59" s="3">
+        <v>54100</v>
+      </c>
+      <c r="K59" s="3">
         <v>71800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>59100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>72300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>56900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>54600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>37300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>35400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>40100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>30400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24800</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4423,68 +4560,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E60" s="3">
         <v>78800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>67900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>70800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>67100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>91500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>77400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>78800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>66300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>78600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>64800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>62800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>42700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>40100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>45900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>52500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>33100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4503,50 +4643,53 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>340500</v>
+        <v>218800</v>
       </c>
       <c r="E61" s="3">
-        <v>340000</v>
+        <v>346900</v>
       </c>
       <c r="F61" s="3">
-        <v>339600</v>
+        <v>347000</v>
       </c>
       <c r="G61" s="3">
-        <v>339400</v>
+        <v>347200</v>
       </c>
       <c r="H61" s="3">
-        <v>339000</v>
+        <v>347500</v>
       </c>
       <c r="I61" s="3">
-        <v>338000</v>
+        <v>347700</v>
       </c>
       <c r="J61" s="3">
+        <v>347400</v>
+      </c>
+      <c r="K61" s="3">
         <v>337500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>337000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>336500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>336000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>335500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>335100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4554,17 +4697,17 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>10000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>69100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>69500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4583,68 +4726,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7100</v>
+        <v>800</v>
       </c>
       <c r="E62" s="3">
-        <v>7600</v>
+        <v>700</v>
       </c>
       <c r="F62" s="3">
-        <v>8200</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>9700</v>
+        <v>600</v>
       </c>
       <c r="H62" s="3">
-        <v>10000</v>
+        <v>800</v>
       </c>
       <c r="I62" s="3">
-        <v>11700</v>
+        <v>600</v>
       </c>
       <c r="J62" s="3">
+        <v>500</v>
+      </c>
+      <c r="K62" s="3">
         <v>12100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15700</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4809,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4743,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4823,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4903,68 +5058,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>306200</v>
+      </c>
+      <c r="E66" s="3">
         <v>426400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>415600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>418500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>416100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>440600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>427100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>428400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>416300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>443600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>425100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>417200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>399300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>53500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>59900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>77000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>122700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>118300</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,8 +5141,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5013,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5093,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5173,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5227,14 +5395,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>227500</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>225500</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5253,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5333,68 +5504,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-619300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-612300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-601100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-594700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-591500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-571200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-552100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-530000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-497000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-466700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-427100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-390100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-355800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-334200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-321900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-313400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-299200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-291100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-280700</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5413,8 +5587,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5493,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5573,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5653,68 +5836,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E76" s="3">
         <v>26100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>65100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>85000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>109900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>138300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>161200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>211100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>215300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>216800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>158500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-270500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-261700</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5733,8 +5919,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5813,79 +6002,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5898,74 +6090,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-11300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-22100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-39600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-37000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-14200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-49900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12300</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,8 +6173,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6008,49 +6206,50 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3500</v>
+        <v>1100</v>
       </c>
       <c r="E83" s="3">
-        <v>3500</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>3500</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>3100</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
-        <v>2900</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>2900</v>
+        <v>800</v>
       </c>
       <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>2800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2800</v>
       </c>
       <c r="M83" s="3">
         <v>2800</v>
       </c>
       <c r="N83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>700</v>
       </c>
       <c r="Q83" s="3">
         <v>700</v>
@@ -6062,20 +6261,20 @@
         <v>700</v>
       </c>
       <c r="T83" s="3">
+        <v>700</v>
+      </c>
+      <c r="U83" s="3">
         <v>1700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6088,8 +6287,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6168,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6248,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6328,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6408,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6488,74 +6702,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>11700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-50800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-40000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6568,8 +6785,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6598,8 +6818,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6607,65 +6828,65 @@
         <v>-1100</v>
       </c>
       <c r="E91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1200</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6678,8 +6899,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6758,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6838,74 +7065,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E94" s="3">
         <v>60300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>26400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-69300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-60200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-94700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>17900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>11000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6918,8 +7148,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6948,31 +7181,32 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7028,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7108,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7188,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7268,74 +7511,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-112100</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>300800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>44500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>160000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>35400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>35500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>17400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7348,31 +7594,34 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7428,74 +7677,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-97300</v>
+      </c>
+      <c r="E102" s="3">
         <v>72200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-119900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-46600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-67300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>192000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-29900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>40600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>153500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>17400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>25000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7506,6 +7758,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
   <si>
     <t>BIGC</t>
   </si>
@@ -656,113 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -775,77 +775,80 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E8" s="3">
         <v>83700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>81800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>80400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>84100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>78000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>75400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>71800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>72400</v>
       </c>
       <c r="L8" s="3">
         <v>72400</v>
       </c>
       <c r="M8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="N8" s="3">
         <v>68200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>66100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>64900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>59300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>49000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>46700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>43100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>39700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>69500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>33200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>112100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>25600</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -858,77 +861,80 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E9" s="3">
         <v>19900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>19100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>18800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>17400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>15300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>7500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -941,77 +947,80 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E10" s="3">
         <v>63800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>62000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>61900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>59000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>56700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>54300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>53900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>54900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>51300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>49000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>48300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>46900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>32900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>54200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>85100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19700</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1024,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,77 +1067,78 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E12" s="3">
         <v>20800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>16500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>10900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>43100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>10800</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,56 +1237,59 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1305,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1304,8 +1323,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1313,16 +1335,16 @@
         <v>2400</v>
       </c>
       <c r="E15" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="F15" s="3">
         <v>2500</v>
       </c>
       <c r="G15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H15" s="3">
         <v>2300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2000</v>
       </c>
       <c r="I15" s="3">
         <v>2000</v>
@@ -1343,14 +1365,14 @@
         <v>2000</v>
       </c>
       <c r="O15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P15" s="3">
         <v>1900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1400</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1366,8 +1388,8 @@
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1387,8 +1409,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,77 +1440,78 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E17" s="3">
         <v>92700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>92400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>88300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>88700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>93400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>92200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>90900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>107100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>103000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>107300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>102200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>98700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>80600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>61300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>56900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>49800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>84300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>40600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>153100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>35900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,77 +1524,80 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-34700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-39100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-7400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-41000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,77 +1644,78 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>4300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,77 +1728,80 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-14800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-29200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-36000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-33400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-31200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-19200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-11500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-13000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-38400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1778,16 +1814,19 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
-      </c>
-      <c r="E22" s="3">
-        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>700</v>
@@ -1820,35 +1859,35 @@
         <v>700</v>
       </c>
       <c r="P22" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1861,77 +1900,80 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-11100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-20200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-18900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-21900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-39600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-34500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-42600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1944,8 +1986,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1953,44 +1998,44 @@
         <v>300</v>
       </c>
       <c r="E24" s="3">
+        <v>300</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>200</v>
       </c>
       <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2012,8 +2057,8 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
+      <c r="Y24" s="3">
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
@@ -2027,8 +2072,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,77 +2158,80 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-19100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-22100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-39600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-37000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-14200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-12500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-42600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,77 +2244,80 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-22100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-39600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-37000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-14200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-49900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,77 +2674,80 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-4300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,77 +2760,80 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-22100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-39600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-37000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-14200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-49900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,77 +2932,80 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-22100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-39600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-37000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-14200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-49900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2940,82 +3018,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,71 +3175,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E41" s="3">
         <v>35400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>133100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>60900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>91600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>220600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>250900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>297600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>364900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>172900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>189600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>219400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>178800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>25400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>33000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3173,76 +3259,79 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E42" s="3">
         <v>133000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>142700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>204300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>198400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>195600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>222900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>221300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>211900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>206100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>138100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>125200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>102300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>43500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>30400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>18400</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3256,71 +3345,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E43" s="3">
         <v>43400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>39300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>37700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>51800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>52200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>59000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>51900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>41000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>33800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>29000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>26100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>22900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>21500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>16100</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3339,8 +3431,11 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3365,8 +3460,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3422,71 +3517,74 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>9100</v>
+        <v>8800</v>
       </c>
       <c r="E45" s="3">
         <v>9100</v>
       </c>
       <c r="F45" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G45" s="3">
         <v>8700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9500</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,71 +3603,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>251200</v>
+      </c>
+      <c r="E46" s="3">
         <v>243500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>355800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>343500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>342000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>341500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>371100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>362900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>374200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>375500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>420000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>433200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>454500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>460500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>243100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>245400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>254100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>212900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>56600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>58600</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,8 +3689,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3614,8 +3718,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3671,71 +3775,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E48" s="3">
         <v>11700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>17600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21200</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3754,53 +3861,56 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E49" s="3">
         <v>71600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>74100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>76700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>79100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>75300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>77300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>79100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>81200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>75400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>77500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>76700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3816,8 +3926,8 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -3837,8 +3947,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,71 +4119,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4086,8 +4205,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,71 +4291,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>340300</v>
+      </c>
+      <c r="E54" s="3">
         <v>335100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>452500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>442500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>444100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>436000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>467500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>461500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>474100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>481400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>528600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>535000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>555500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>560500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>266500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>268800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>276600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>235500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>79600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>82000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4252,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,71 +4443,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
         <v>8100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4397,35 +4527,38 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3000</v>
       </c>
-      <c r="G58" s="3">
-        <v>3100</v>
-      </c>
       <c r="H58" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I58" s="3">
         <v>2900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4438,8 +4571,8 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4451,16 +4584,16 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>11900</v>
-      </c>
-      <c r="U58" s="3">
-        <v>2200</v>
       </c>
       <c r="V58" s="3">
         <v>2200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>2200</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4480,71 +4613,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E59" s="3">
         <v>60900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>42600</v>
+      </c>
+      <c r="I59" s="3">
         <v>42300</v>
       </c>
-      <c r="H59" s="3">
-        <v>42300</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>65800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>54100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>59100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>72300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>54600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>37300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>35400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>40100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>35000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>30400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>24800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4563,71 +4699,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E60" s="3">
         <v>86600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>78800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>67900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>70800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>67100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>91500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>77400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>78800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>66300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>78600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>64800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>62800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>48800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>42700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>40100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>45900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>52500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>33100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4646,53 +4785,56 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>218100</v>
+      </c>
+      <c r="E61" s="3">
         <v>218800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>346900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>347000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>347200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>347500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>347700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>347400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>337500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>337000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>336500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>336000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>335500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>335100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4700,17 +4842,17 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>10000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>69100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>69500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4729,8 +4871,11 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4738,62 +4883,62 @@
         <v>800</v>
       </c>
       <c r="E62" s="3">
+        <v>800</v>
+      </c>
+      <c r="F62" s="3">
         <v>700</v>
-      </c>
-      <c r="F62" s="3">
-        <v>600</v>
       </c>
       <c r="G62" s="3">
         <v>600</v>
       </c>
       <c r="H62" s="3">
+        <v>600</v>
+      </c>
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>12100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>12800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>14000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15700</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +4957,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,71 +5215,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>306900</v>
+      </c>
+      <c r="E66" s="3">
         <v>306200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>426400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>415600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>418500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>416100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>440600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>427100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>428400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>416300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>443600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>425100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>417200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>399300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>55400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>53500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>77000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>122700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>118300</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5144,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5505,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5398,14 +5565,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>227500</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>225500</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5424,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,71 +5677,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-621700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-619300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-612300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-601100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-594700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-591500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-571200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-552100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-530000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-497000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-466700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-427100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-390100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-355800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-334200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-321900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-313400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-299200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-291100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-280700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5590,8 +5763,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,71 +6021,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E76" s="3">
         <v>29000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>26100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>26900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>65100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>85000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>109900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>138300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>161200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>211100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>215300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>216800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>158500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-270500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-261700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5922,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,82 +6193,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6093,77 +6284,80 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-22100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-39600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-37000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-14200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-49900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6176,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,52 +6404,53 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>900</v>
       </c>
       <c r="F83" s="3">
         <v>900</v>
       </c>
       <c r="G83" s="3">
+        <v>900</v>
+      </c>
+      <c r="H83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>2800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2800</v>
       </c>
       <c r="N83" s="3">
         <v>2800</v>
       </c>
       <c r="O83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="P83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>700</v>
       </c>
       <c r="R83" s="3">
         <v>700</v>
@@ -6264,20 +6462,20 @@
         <v>700</v>
       </c>
       <c r="U83" s="3">
+        <v>700</v>
+      </c>
+      <c r="V83" s="3">
         <v>1700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>500</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6290,8 +6488,11 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,77 +6918,80 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E89" s="3">
         <v>5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>11700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-31400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-50800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-22000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-40000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6788,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,77 +7038,78 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="E91" s="3">
         <v>-1100</v>
       </c>
       <c r="F91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6902,8 +7122,11 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,77 +7294,80 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E94" s="3">
         <v>9300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>60300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>26400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-69300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-24800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-60200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-94700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>17900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>11000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7151,8 +7380,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7414,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7208,8 +7441,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7265,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,77 +7756,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-112100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>300800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>44500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>160000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>35400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>35500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>17400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7597,8 +7842,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7623,8 +7871,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7680,77 +7928,80 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-97300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>72200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-10800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-119900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-46600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-67300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>192000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-29900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>40600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>153500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>17400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>25000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7761,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BIGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>BIGC</t>
   </si>
@@ -656,116 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -778,80 +779,83 @@
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E8" s="3">
         <v>87000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>83700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>81800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>80400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>84100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>78000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>75400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>72400</v>
       </c>
       <c r="M8" s="3">
         <v>72400</v>
       </c>
       <c r="N8" s="3">
+        <v>72400</v>
+      </c>
+      <c r="O8" s="3">
         <v>68200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>66100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>64900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>59300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>49000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>46700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>43100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>39700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>69500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>33200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>112100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>25600</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,80 +868,83 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E9" s="3">
         <v>19500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>19800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>18900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>19100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>17400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>17100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>15300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -950,80 +957,83 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>65400</v>
+      </c>
+      <c r="E10" s="3">
         <v>67600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>63800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>62000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>61900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>59000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>56700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>54300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>53900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>54900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>51300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>49000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>48300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>46900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>37500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>32900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>31100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>54200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>25700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>85100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>19700</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1046,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,80 +1081,81 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E12" s="3">
         <v>19800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>22200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>22400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>16500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>22300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>10900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>43100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10800</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1168,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,59 +1257,62 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E14" s="3">
         <v>1600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1308,8 +1328,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1326,28 +1346,31 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="E15" s="3">
         <v>2400</v>
       </c>
       <c r="F15" s="3">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="G15" s="3">
         <v>2500</v>
       </c>
       <c r="H15" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I15" s="3">
         <v>2300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2000</v>
       </c>
       <c r="J15" s="3">
         <v>2000</v>
@@ -1368,14 +1391,14 @@
         <v>2000</v>
       </c>
       <c r="P15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1400</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1391,8 +1414,8 @@
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1412,8 +1435,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1441,80 +1467,81 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E17" s="3">
         <v>86200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>92700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>92400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>88300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>88700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>93400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>92200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>90900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>107100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>103000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>107300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>102200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>98700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>80600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>61300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>56900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>49800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>84300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>40600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>153100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>35900</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1527,80 +1554,83 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-34700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-30600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-39100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-36100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-14800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-7400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1613,8 +1643,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1645,80 +1678,81 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1731,80 +1765,83 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E21" s="3">
         <v>2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-14800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-29200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-33400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-19200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-11500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-13000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,19 +1854,22 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>2700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>700</v>
       </c>
       <c r="G22" s="3">
         <v>700</v>
@@ -1862,35 +1902,35 @@
         <v>700</v>
       </c>
       <c r="Q22" s="3">
+        <v>700</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,80 +1943,83 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-18900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-30200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1989,56 +2032,59 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E24" s="3">
         <v>300</v>
       </c>
       <c r="F24" s="3">
+        <v>300</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>200</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
       </c>
       <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2060,8 +2106,8 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
+      <c r="Z24" s="3">
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
@@ -2075,8 +2121,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2161,80 +2210,83 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-7000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-19100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-22100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-39600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-14200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2247,80 +2299,83 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-22100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-39600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-14200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-49900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,8 +2388,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,8 +2477,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2505,8 +2566,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2591,8 +2655,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2677,80 +2744,83 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2763,80 +2833,83 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-22100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-39600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-14200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-49900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2849,8 +2922,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2935,80 +3011,83 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-22100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-39600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-14200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-49900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3021,85 +3100,88 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3194,11 @@
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3144,8 +3229,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3176,74 +3262,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E41" s="3">
         <v>88900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>133100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>60900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>61100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>220600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>250900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>297600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>364900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>172900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>189600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>219400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>178800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>25400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>33000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3262,79 +3349,82 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E42" s="3">
         <v>89300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>133000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>142700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>204300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>198400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>195600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>222900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>221300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>211900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>206100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>138100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>125200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>102300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>43500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>30400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18400</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3348,74 +3438,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E43" s="3">
         <v>48100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>43400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>45100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>39300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>37700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>51800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>59000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>48100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>45900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>41000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>39800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>33800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>29000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>26100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>22900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>21500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>20200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>16100</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3434,8 +3527,11 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3463,8 +3559,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3520,74 +3616,77 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E45" s="3">
         <v>8800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9100</v>
       </c>
       <c r="F45" s="3">
         <v>9100</v>
       </c>
       <c r="G45" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H45" s="3">
         <v>8700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>8300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9500</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,74 +3705,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192700</v>
+      </c>
+      <c r="E46" s="3">
         <v>251200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>355800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>343500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>342000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>341500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>371100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>362900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>374200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>375500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>420000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>433200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>454500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>460500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>243100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>245400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>254100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>212900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>56600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>58600</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3692,8 +3794,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3721,8 +3826,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3778,74 +3883,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E48" s="3">
         <v>11100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>17600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,56 +3972,59 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E49" s="3">
         <v>69200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>74100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>76700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>79100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>75300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>77300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>79100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>81200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>77500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>76700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,8 +4040,8 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3950,8 +4061,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4036,8 +4150,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4122,74 +4239,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>3100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,8 +4328,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4294,74 +4417,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>286300</v>
+      </c>
+      <c r="E54" s="3">
         <v>340300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>335100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>452500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>442500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>444100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>436000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>467500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>461500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>474100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>481400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>528600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>535000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>555500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>560500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>266500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>268800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>276600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>235500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>79600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>82000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4380,8 +4506,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4412,8 +4541,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4444,74 +4574,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,38 +4661,41 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4574,8 +4708,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4587,16 +4721,16 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>11900</v>
-      </c>
-      <c r="V58" s="3">
-        <v>2200</v>
       </c>
       <c r="W58" s="3">
         <v>2200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>2200</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4616,74 +4750,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E59" s="3">
         <v>56600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>60900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>65800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>59100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>56900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>54600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>42900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>37300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>35400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>40100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>35000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>30400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>24800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,74 +4839,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E60" s="3">
         <v>88000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>78800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>67900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>70800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>67100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>91500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>77400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>78800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>78600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>64800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>62800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>48800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>42700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>40100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>45900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>52500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>33100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,56 +4928,59 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E61" s="3">
         <v>218100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>218800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>346900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>347000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>347200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>347500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>347700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>347400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>337500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>337000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>336500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>336000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>335500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>335100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4845,17 +4988,17 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>10000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>69100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>69500</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4874,74 +5017,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
         <v>800</v>
       </c>
       <c r="F62" s="3">
+        <v>800</v>
+      </c>
+      <c r="G62" s="3">
         <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>600</v>
       </c>
       <c r="H62" s="3">
         <v>600</v>
       </c>
       <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>12800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>14500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15700</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4960,8 +5106,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5046,8 +5195,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5132,8 +5284,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5218,74 +5373,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>248200</v>
+      </c>
+      <c r="E66" s="3">
         <v>306900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>306200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>426400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>415600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>418500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>416100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>440600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>427100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>428400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>416300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>443600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>425100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>417200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>399300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>53500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>59900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>77000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>122700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>118300</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5304,8 +5462,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5336,8 +5497,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5422,8 +5584,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5508,8 +5673,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5568,14 +5736,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>227500</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>225500</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5594,8 +5762,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5680,74 +5851,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-622000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-621700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-619300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-612300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-601100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-594700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-591500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-571200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-552100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-530000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-497000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-466700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-427100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-390100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-355800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-334200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-321900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-313400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-299200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-291100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-280700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5766,8 +5940,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5852,8 +6029,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5938,8 +6118,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6024,74 +6207,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38100</v>
+      </c>
+      <c r="E76" s="3">
         <v>33400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>29000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>26100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>26900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>26900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>65100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>85000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>109900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>138300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>161200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>211100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>215300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>216800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>158500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-270500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-261700</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6110,8 +6296,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6196,85 +6385,88 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6287,80 +6479,83 @@
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-22100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-39600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-14200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-49900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12300</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6373,8 +6568,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6405,55 +6603,56 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>900</v>
       </c>
       <c r="G83" s="3">
         <v>900</v>
       </c>
       <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
         <v>800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>2800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>2800</v>
       </c>
       <c r="O83" s="3">
         <v>2800</v>
       </c>
       <c r="P83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>700</v>
       </c>
       <c r="S83" s="3">
         <v>700</v>
@@ -6465,20 +6664,20 @@
         <v>700</v>
       </c>
       <c r="V83" s="3">
+        <v>700</v>
+      </c>
+      <c r="W83" s="3">
         <v>1700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6491,8 +6690,11 @@
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6577,8 +6779,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6663,8 +6868,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6749,8 +6957,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6835,8 +7046,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6921,80 +7135,83 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>12400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>11700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-31400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-50800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-22000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-40000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7007,8 +7224,11 @@
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7039,8 +7259,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7048,71 +7269,71 @@
         <v>-800</v>
       </c>
       <c r="E91" s="3">
-        <v>-1100</v>
+        <v>-800</v>
       </c>
       <c r="F91" s="3">
         <v>-1100</v>
       </c>
       <c r="G91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7125,8 +7346,11 @@
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7211,8 +7435,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7297,80 +7524,83 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E94" s="3">
         <v>42600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>9300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>60300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>26400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-69300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-24800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-60200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-94700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>17900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>11000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7383,8 +7613,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7415,8 +7648,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7444,8 +7678,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7501,8 +7735,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7587,8 +7824,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7673,8 +7913,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7759,80 +8002,83 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-112100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>300800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>44500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>160000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>35400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>35500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>17400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3400</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7845,8 +8091,11 @@
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7874,8 +8123,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7931,80 +8180,83 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E102" s="3">
         <v>53400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-97300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>72200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-119900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-30200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-46600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-67300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>192000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-29900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>40600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>153500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>17400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>25000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8015,6 +8267,9 @@
         <v>3</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
